--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487094_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487094_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7849</v>
+        <v>6.6352</v>
       </c>
       <c r="E2" t="n">
-        <v>2.514</v>
+        <v>2.7926</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2709</v>
+        <v>3.8426</v>
       </c>
       <c r="G2" t="n">
         <v>4.7881</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.846</v>
+        <v>0.6963</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3291</v>
+        <v>-0.0505</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1752</v>
+        <v>0.7469</v>
       </c>
       <c r="V2" t="n">
         <v>0.5717</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3929</v>
+        <v>3.0439</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1502</v>
+        <v>2.828</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2427</v>
+        <v>0.216</v>
       </c>
       <c r="G3" t="n">
         <v>7.2698</v>
@@ -688,13 +688,13 @@
         <v>0.579</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9181</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6504</v>
+        <v>0.3282</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2677</v>
+        <v>0.2409</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5138</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.214</v>
+        <v>2.3879</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2554</v>
+        <v>1.1349</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9586</v>
+        <v>1.2531</v>
       </c>
       <c r="G4" t="n">
         <v>4.2253</v>
@@ -766,13 +766,13 @@
         <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7833</v>
+        <v>0.3906</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6848</v>
+        <v>0.1947</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0985</v>
+        <v>0.1959</v>
       </c>
       <c r="V4" t="n">
         <v>-1.842</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8072</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.1925</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2641</v>
+        <v>0.6148</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0295</v>
+        <v>0.5738</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2833</v>
+        <v>2.3567</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2538</v>
+        <v>-1.7829</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9036</v>
+        <v>-0.7018</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6041</v>
+        <v>1.8629</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7004</v>
+        <v>-2.5647</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8741</v>
+        <v>1.2757</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3207</v>
+        <v>0.4938</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5534</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6015</v>
+        <v>0.4614</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6214</v>
+        <v>0.2803</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0198</v>
+        <v>0.1811</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6407</v>
+        <v>0.4969</v>
       </c>
       <c r="E6" t="n">
-        <v>0.133</v>
+        <v>0.0186</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5077</v>
+        <v>0.4783</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5738</v>
+        <v>0.0295</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3567</v>
+        <v>1.2833</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7829</v>
+        <v>-1.2538</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7018</v>
+        <v>0.9036</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8629</v>
+        <v>1.6041</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.5647</v>
+        <v>-0.7004</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2757</v>
+        <v>-0.8741</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4938</v>
+        <v>-0.3207</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7818000000000001</v>
+        <v>-0.5534</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2948</v>
+        <v>0.2743</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2208</v>
+        <v>0.08</v>
       </c>
       <c r="U6" t="n">
-        <v>0.074</v>
+        <v>0.1943</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1218</v>
+        <v>-0.5164</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7701</v>
+        <v>-1.1112</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6483</v>
+        <v>0.5948</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9467</v>
@@ -1000,13 +1000,13 @@
         <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6319</v>
+        <v>0.2373</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5037</v>
+        <v>0.1626</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1282</v>
+        <v>0.0747</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.929</v>
+        <v>-0.698</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2851</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3561</v>
+        <v>0.0081</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4703</v>
@@ -1078,13 +1078,13 @@
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1553</v>
+        <v>0.3863</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9518</v>
+        <v>-0.3728</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1071</v>
+        <v>0.7591</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0687</v>
+        <v>-1.0023</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7134</v>
+        <v>-1.754</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.7517</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3767</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.115</v>
+        <v>0.1814</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1057</v>
+        <v>-0.1464</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2208</v>
+        <v>0.3278</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2251</v>
+        <v>-1.1319</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7721</v>
+        <v>-0.8128</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4529</v>
+        <v>-0.3191</v>
       </c>
       <c r="G10" t="n">
         <v>-1.709</v>
@@ -1234,13 +1234,13 @@
         <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0601</v>
+        <v>0.0331</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2842</v>
+        <v>-0.3249</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2241</v>
+        <v>0.3579</v>
       </c>
       <c r="V10" t="n">
         <v>-0.614</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3143</v>
+        <v>-2.6351</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5816</v>
+        <v>-4.9024</v>
       </c>
       <c r="F11" t="n">
         <v>2.2673</v>
@@ -1312,10 +1312,10 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3398</v>
+        <v>0.3394</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6253</v>
+        <v>0.0539</v>
       </c>
       <c r="U11" t="n">
         <v>0.2855</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.197700000000003</v>
+        <v>7.387400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5097</v>
+        <v>-2.319900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>9.707500000000001</v>
+        <v>9.707600000000001</v>
       </c>
       <c r="G12" t="n">
         <v>13.6205</v>
@@ -1360,7 +1360,7 @@
         <v>16.9583</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.337999999999999</v>
+        <v>-3.338</v>
       </c>
       <c r="J12" t="n">
         <v>10.2776</v>
@@ -1390,13 +1390,13 @@
         <v>8.6852</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3794</v>
+        <v>3.5692</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9845999999999999</v>
+        <v>0.2050999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3643</v>
+        <v>3.3641</v>
       </c>
       <c r="V12" t="n">
         <v>-4.0121</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4132</v>
+        <v>3.6858</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0473</v>
+        <v>2.9458</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3659</v>
+        <v>0.74</v>
       </c>
       <c r="G13" t="n">
         <v>0.0658</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0193</v>
+        <v>0.2918</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2427</v>
+        <v>0.1412</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2234</v>
+        <v>0.1507</v>
       </c>
       <c r="V13" t="n">
         <v>2.1701</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5841</v>
+        <v>1.7646</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0279</v>
+        <v>1.128</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5562</v>
+        <v>0.6365</v>
       </c>
       <c r="G14" t="n">
         <v>2.5551</v>
@@ -1546,13 +1546,13 @@
         <v>0.386</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.392</v>
+        <v>-0.2115</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5354</v>
+        <v>-0.4352</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1434</v>
+        <v>0.2237</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1401</v>
+        <v>0.9086</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.092</v>
+        <v>-0.391</v>
       </c>
       <c r="F15" t="n">
-        <v>0.952</v>
+        <v>1.2996</v>
       </c>
       <c r="G15" t="n">
         <v>-1.2206</v>
@@ -1624,13 +1624,13 @@
         <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6987</v>
+        <v>-0.6501</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5467</v>
+        <v>-0.8457</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1521</v>
+        <v>0.1956</v>
       </c>
       <c r="V15" t="n">
         <v>0.6562</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6317</v>
+        <v>0.1082</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.236</v>
+        <v>-0.2275</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3958</v>
+        <v>0.3358</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3718</v>
+        <v>-1.2012</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5556</v>
+        <v>-1.6539</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1838</v>
+        <v>0.4527</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1781</v>
+        <v>0.3802</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3002</v>
+        <v>-0.2381</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1221</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1936</v>
+        <v>-1.5814</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2554</v>
+        <v>-1.4157</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0617</v>
+        <v>-0.1657</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8752</v>
+        <v>-0.4276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6214</v>
+        <v>-0.6077</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2538</v>
+        <v>0.1801</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8066</v>
+        <v>-1.0451</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9285</v>
+        <v>-0.4989</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1219</v>
+        <v>-0.5461</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2012</v>
+        <v>-2.1539</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6539</v>
+        <v>-2.0711</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4527</v>
+        <v>-0.0828</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3802</v>
+        <v>-0.4384</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2381</v>
+        <v>0.0257</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6183999999999999</v>
+        <v>-0.4641</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5814</v>
+        <v>-1.7155</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4157</v>
+        <v>-2.0968</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1657</v>
+        <v>0.3813</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3425</v>
+        <v>-0.428</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3087</v>
+        <v>-0.2812</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0337</v>
+        <v>-0.1468</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1879</v>
+        <v>-1.0832</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5804</v>
+        <v>-2.3722</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3925</v>
+        <v>1.289</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1876</v>
+        <v>-0.6902</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5143</v>
+        <v>-0.858</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6733</v>
+        <v>0.1678</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7263</v>
+        <v>-1.191</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4489</v>
+        <v>-0.5641</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.1752</v>
+        <v>-0.6269</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4613</v>
+        <v>0.5008</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9632</v>
+        <v>-0.2939</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5019</v>
+        <v>0.7947</v>
       </c>
       <c r="P18" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8646</v>
+        <v>-0.0069</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.152</v>
+        <v>-0.2161</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0165</v>
+        <v>0.2092</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2567</v>
+        <v>-1.4329</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5725</v>
+        <v>-1.0371</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3158</v>
+        <v>-0.3958</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6902</v>
+        <v>-0.3718</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.858</v>
+        <v>-1.5556</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1678</v>
+        <v>1.1838</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.191</v>
+        <v>-0.1781</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5641</v>
+        <v>-0.3002</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6269</v>
+        <v>0.1221</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5008</v>
+        <v>-0.1936</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2939</v>
+        <v>-1.2554</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7947</v>
+        <v>1.0617</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1805</v>
+        <v>0.074</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4164</v>
+        <v>-0.1798</v>
       </c>
       <c r="U19" t="n">
-        <v>0.236</v>
+        <v>0.2538</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5861</v>
+        <v>-1.5961</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7994</v>
+        <v>-2.8808</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7867</v>
+        <v>1.2847</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1539</v>
+        <v>-3.1876</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0711</v>
+        <v>-0.5143</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0828</v>
+        <v>-2.6733</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4384</v>
+        <v>-1.7263</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0257</v>
+        <v>1.4489</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4641</v>
+        <v>-3.1752</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7155</v>
+        <v>-1.4613</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0968</v>
+        <v>-1.9632</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3813</v>
+        <v>0.5019</v>
       </c>
       <c r="P20" t="n">
-        <v>0.965</v>
+        <v>0.193</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.969</v>
+        <v>0.4564</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5816</v>
+        <v>-0.4524</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3874</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5717</v>
+        <v>0.9421</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1857</v>
+        <v>1.228</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.614</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5928</v>
+        <v>-1.8981</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0647</v>
+        <v>-1.6642</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.528</v>
+        <v>-0.2339</v>
       </c>
       <c r="G21" t="n">
         <v>-1.562</v>
@@ -2092,13 +2092,13 @@
         <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7099</v>
+        <v>-0.0152</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4759</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.234</v>
+        <v>0.0601</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9932</v>
+        <v>-4.2745</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5093</v>
+        <v>-4.7095</v>
       </c>
       <c r="F22" t="n">
-        <v>0.516</v>
+        <v>0.4351</v>
       </c>
       <c r="G22" t="n">
         <v>-5.8541</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>0.154</v>
+        <v>-0.1272</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2115</v>
+        <v>-0.4118</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3655</v>
+        <v>0.2845</v>
       </c>
       <c r="V22" t="n">
         <v>1.5138</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.197799999999999</v>
+        <v>-4.862699999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.707599999999999</v>
+        <v>-9.7074</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5098</v>
+        <v>4.8449</v>
       </c>
       <c r="G23" t="n">
         <v>-13.6205</v>
@@ -2239,7 +2239,7 @@
         <v>5.1479</v>
       </c>
       <c r="P23" t="n">
-        <v>5.7902</v>
+        <v>5.790199999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-8.6852</v>
@@ -2248,13 +2248,13 @@
         <v>14.4756</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.3795</v>
+        <v>-1.0443</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.3641</v>
+        <v>-3.364</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9845999999999999</v>
+        <v>2.3197</v>
       </c>
       <c r="V23" t="n">
         <v>4.0119</v>
